--- a/Sedes_a_priorizar_Totoro_2.xlsx
+++ b/Sedes_a_priorizar_Totoro_2.xlsx
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>73.78767650862069</v>
+        <v>73.79679935344828</v>
       </c>
     </row>
   </sheetData>
